--- a/initializationData/GliderMission.xlsx
+++ b/initializationData/GliderMission.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showObjects="none" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laytonc\Documents\GitHub\gliderMetadata\initializationData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EF9605-7572-4808-A127-F2C25BC44C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB0107D-5198-4088-8CFB-A69843037E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="913">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2729,6 +2729,21 @@
     <t>Back from maintenance seal trial, First mission with thrusters</t>
   </si>
   <si>
+    <t>20260120</t>
+  </si>
+  <si>
+    <t>20251216</t>
+  </si>
+  <si>
+    <t>241970</t>
+  </si>
+  <si>
+    <t>20260312</t>
+  </si>
+  <si>
+    <t>20260220</t>
+  </si>
+  <si>
     <t>Microrider probes cal date</t>
   </si>
   <si>
@@ -2754,6 +2769,30 @@
   </si>
   <si>
     <t>Back from maintenance seal trial, Eco needs to be calibration, CDOM values weird compare to SEA021</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA021_092</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA019_151</t>
+  </si>
+  <si>
+    <t>GL1-GL2-HL4-GL2-HL3-GL1-TRI-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>Halmar/ Sigma-T</t>
+  </si>
+  <si>
+    <t>512hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First microrider/ADCP/Tridente mission, statistic period too big changed mid mission,  linear issue where actuator doesn't follow command because of quick inflection, lots of navigation tests. Lost MR data 5 times, fixed with MR OFF/ON. Glider touch bottom the day of recovery and broke a probe </t>
+  </si>
+  <si>
+    <t>Thruster piloting tests</t>
+  </si>
+  <si>
+    <t>SEA220</t>
   </si>
 </sst>
 </file>
@@ -3858,85 +3897,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DR106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:DR108"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" customWidth="1"/>
-    <col min="3" max="4" width="15.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="4.08984375" customWidth="1"/>
+    <col min="3" max="4" width="15.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" style="4" customWidth="1"/>
     <col min="7" max="7" width="14" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.77734375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.81640625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7" style="7" customWidth="1"/>
-    <col min="16" max="16" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.77734375" style="7" customWidth="1"/>
-    <col min="18" max="18" width="10.21875" style="7" customWidth="1"/>
-    <col min="19" max="19" width="78.77734375" customWidth="1"/>
-    <col min="20" max="20" width="8.21875" customWidth="1"/>
-    <col min="21" max="21" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.81640625" style="7" customWidth="1"/>
+    <col min="18" max="18" width="10.1796875" style="7" customWidth="1"/>
+    <col min="19" max="19" width="78.81640625" customWidth="1"/>
+    <col min="20" max="20" width="8.1796875" customWidth="1"/>
+    <col min="21" max="21" width="20.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.77734375" customWidth="1"/>
-    <col min="24" max="24" width="11.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.81640625" customWidth="1"/>
+    <col min="24" max="24" width="11.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="20" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20.5546875" style="77" customWidth="1"/>
-    <col min="30" max="30" width="20.5546875" style="77" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.77734375" style="7" customWidth="1"/>
-    <col min="32" max="34" width="20.5546875" style="77" customWidth="1"/>
-    <col min="35" max="35" width="24.88671875" style="77" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.54296875" style="77" customWidth="1"/>
+    <col min="30" max="30" width="20.54296875" style="77" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.81640625" style="7" customWidth="1"/>
+    <col min="32" max="34" width="20.54296875" style="77" customWidth="1"/>
+    <col min="35" max="35" width="24.90625" style="77" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="10" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.5546875" style="7" customWidth="1"/>
-    <col min="42" max="42" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.5546875" style="7" customWidth="1"/>
-    <col min="44" max="44" width="7.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.44140625" style="78" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="16.77734375" style="78" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="11.77734375" style="78" customWidth="1"/>
-    <col min="52" max="52" width="12.77734375" style="78" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="12.77734375" style="78" customWidth="1"/>
-    <col min="54" max="54" width="11.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.77734375" style="6" customWidth="1"/>
-    <col min="57" max="58" width="12.77734375" style="78" customWidth="1"/>
-    <col min="59" max="59" width="11.77734375" style="78" customWidth="1"/>
-    <col min="60" max="60" width="14.77734375" style="78" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="15.21875" style="78" bestFit="1" customWidth="1"/>
-    <col min="62" max="64" width="15.21875" style="78" customWidth="1"/>
+    <col min="38" max="38" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="7" customWidth="1"/>
+    <col min="42" max="42" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.54296875" style="7" customWidth="1"/>
+    <col min="44" max="44" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.453125" style="78" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="13.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="16.81640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.81640625" style="78" customWidth="1"/>
+    <col min="52" max="52" width="12.81640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="12.81640625" style="78" customWidth="1"/>
+    <col min="54" max="54" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.81640625" style="6" customWidth="1"/>
+    <col min="57" max="58" width="12.81640625" style="78" customWidth="1"/>
+    <col min="59" max="59" width="11.81640625" style="78" customWidth="1"/>
+    <col min="60" max="60" width="14.81640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
+    <col min="62" max="64" width="15.1796875" style="78" customWidth="1"/>
     <col min="65" max="65" width="17" style="78" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="17.77734375" style="6" customWidth="1"/>
-    <col min="68" max="75" width="15.21875" style="78" customWidth="1"/>
-    <col min="76" max="76" width="23.5546875" style="78" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="11.77734375" style="5" customWidth="1"/>
-    <col min="78" max="81" width="16.33203125" style="1" customWidth="1"/>
-    <col min="82" max="82" width="12.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="12.77734375" style="6" customWidth="1"/>
+    <col min="66" max="67" width="17.81640625" style="6" customWidth="1"/>
+    <col min="68" max="75" width="15.1796875" style="78" customWidth="1"/>
+    <col min="76" max="76" width="23.54296875" style="78" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.81640625" style="5" customWidth="1"/>
+    <col min="78" max="81" width="16.36328125" style="1" customWidth="1"/>
+    <col min="82" max="82" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.81640625" style="6" customWidth="1"/>
     <col min="84" max="84" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="7.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="25.77734375" style="7" customWidth="1"/>
-    <col min="90" max="90" width="64.44140625" style="7" customWidth="1"/>
-    <col min="91" max="91" width="78.77734375" style="8" customWidth="1"/>
+    <col min="89" max="89" width="25.81640625" style="7" customWidth="1"/>
+    <col min="90" max="90" width="64.453125" style="7" customWidth="1"/>
+    <col min="91" max="91" width="78.81640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="24"/>
       <c r="D1" s="146" t="s">
         <v>797</v>
@@ -4020,7 +4059,7 @@
       <c r="CL1" s="25"/>
       <c r="CM1" s="30"/>
     </row>
-    <row r="2" spans="1:91" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:91" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C2" s="64" t="s">
         <v>0</v>
       </c>
@@ -4208,7 +4247,7 @@
         <v>770</v>
       </c>
       <c r="BM2" s="161" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="BN2" s="72" t="s">
         <v>848</v>
@@ -4241,7 +4280,7 @@
         <v>856</v>
       </c>
       <c r="BX2" s="161" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="BY2" s="73" t="s">
         <v>167</v>
@@ -4289,7 +4328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="124">
         <v>1</v>
       </c>
@@ -4491,7 +4530,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="124">
         <v>2</v>
       </c>
@@ -4695,7 +4734,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="136">
         <v>3</v>
       </c>
@@ -4899,7 +4938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="136">
         <v>4</v>
       </c>
@@ -5104,7 +5143,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="136">
         <v>5</v>
       </c>
@@ -5310,7 +5349,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="136">
         <v>6</v>
       </c>
@@ -5514,7 +5553,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="136">
         <v>7</v>
       </c>
@@ -5718,7 +5757,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="136">
         <v>8</v>
       </c>
@@ -5922,7 +5961,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="136">
         <v>9</v>
       </c>
@@ -6126,7 +6165,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="136">
         <v>10</v>
       </c>
@@ -6334,7 +6373,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="136">
         <v>11</v>
       </c>
@@ -6540,7 +6579,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="136">
         <v>12</v>
       </c>
@@ -6744,7 +6783,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="136">
         <v>13</v>
       </c>
@@ -6952,7 +6991,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="136">
         <v>14</v>
       </c>
@@ -7158,7 +7197,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="136">
         <v>15</v>
       </c>
@@ -7363,7 +7402,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="124">
         <v>16</v>
       </c>
@@ -7568,7 +7607,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="124">
         <v>17</v>
       </c>
@@ -7767,7 +7806,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="124">
         <v>18</v>
       </c>
@@ -7972,7 +8011,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="124">
         <v>18</v>
       </c>
@@ -8178,7 +8217,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="124">
         <v>19</v>
       </c>
@@ -8384,7 +8423,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="124">
         <v>20</v>
       </c>
@@ -8590,7 +8629,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="124">
         <v>21</v>
       </c>
@@ -8794,7 +8833,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="124">
         <v>22</v>
       </c>
@@ -8997,7 +9036,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="26" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="124">
         <v>23</v>
       </c>
@@ -9204,7 +9243,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="124">
         <v>24</v>
       </c>
@@ -9407,7 +9446,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="124">
         <v>25</v>
       </c>
@@ -9613,7 +9652,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="124">
         <v>26</v>
       </c>
@@ -9802,7 +9841,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="124">
         <v>27</v>
       </c>
@@ -10008,7 +10047,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="124">
         <v>28</v>
       </c>
@@ -10213,7 +10252,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="124">
         <v>29</v>
       </c>
@@ -10421,7 +10460,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="124"/>
       <c r="C33" s="47" t="s">
         <v>246</v>
@@ -10521,7 +10560,7 @@
       <c r="CL33" s="37"/>
       <c r="CM33" s="43"/>
     </row>
-    <row r="34" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="124"/>
       <c r="C34" s="47" t="s">
         <v>247</v>
@@ -10621,7 +10660,7 @@
       <c r="CL34" s="37"/>
       <c r="CM34" s="43"/>
     </row>
-    <row r="35" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="124">
         <v>30</v>
       </c>
@@ -10827,7 +10866,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="36" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="124">
         <v>31</v>
       </c>
@@ -11034,7 +11073,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="124">
         <v>32</v>
       </c>
@@ -11229,7 +11268,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="38" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="124">
         <v>33</v>
       </c>
@@ -11435,7 +11474,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="39" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="124">
         <v>34</v>
       </c>
@@ -11641,7 +11680,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="40" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="124">
         <v>35</v>
       </c>
@@ -11849,7 +11888,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="124">
         <v>36</v>
       </c>
@@ -12064,7 +12103,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="124">
         <v>37</v>
       </c>
@@ -12269,7 +12308,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="43" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="124">
         <v>38</v>
       </c>
@@ -12472,7 +12511,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="124">
         <v>39</v>
       </c>
@@ -12679,7 +12718,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="45" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="124">
         <v>40</v>
       </c>
@@ -12884,7 +12923,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="46" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="124">
         <v>41</v>
       </c>
@@ -13090,7 +13129,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="124">
         <v>42</v>
       </c>
@@ -13295,7 +13334,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="48" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="124">
         <v>43</v>
       </c>
@@ -13500,7 +13539,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="49" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="124">
         <v>44</v>
       </c>
@@ -13714,7 +13753,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="124">
         <v>45</v>
       </c>
@@ -13919,7 +13958,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="51" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="124">
         <v>46</v>
       </c>
@@ -14124,7 +14163,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="52" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="124">
         <v>47</v>
       </c>
@@ -14338,7 +14377,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="124">
         <v>48</v>
       </c>
@@ -14553,7 +14592,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="54" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="124">
         <v>49</v>
       </c>
@@ -14760,7 +14799,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="55" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="124">
         <v>50</v>
       </c>
@@ -14967,7 +15006,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="56" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="124">
         <v>51</v>
       </c>
@@ -15187,7 +15226,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="124">
         <v>52</v>
       </c>
@@ -15393,7 +15432,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="58" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="124">
         <v>53</v>
       </c>
@@ -15598,7 +15637,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="59" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="124">
         <v>54</v>
       </c>
@@ -15815,7 +15854,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="60" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="124">
         <v>55</v>
       </c>
@@ -16020,7 +16059,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="61" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="124">
         <v>56</v>
       </c>
@@ -16225,7 +16264,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="62" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="124">
         <v>57</v>
       </c>
@@ -16440,7 +16479,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="63" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="124">
         <v>58</v>
       </c>
@@ -16651,7 +16690,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="64" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="124">
         <v>59</v>
       </c>
@@ -16856,7 +16895,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="65" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="124">
         <v>60</v>
       </c>
@@ -17070,7 +17109,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="66" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="124">
         <v>61</v>
       </c>
@@ -17278,7 +17317,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="124">
         <v>62</v>
       </c>
@@ -17486,7 +17525,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="68" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="124">
         <v>63</v>
       </c>
@@ -17704,7 +17743,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="69" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="124">
         <v>64</v>
       </c>
@@ -17910,7 +17949,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="1:122" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:122" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="124">
         <v>65</v>
       </c>
@@ -18124,7 +18163,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="71" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="124">
         <v>66</v>
       </c>
@@ -18369,7 +18408,7 @@
       <c r="DQ71" s="88"/>
       <c r="DR71" s="88"/>
     </row>
-    <row r="72" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="124">
         <v>67</v>
       </c>
@@ -18607,7 +18646,7 @@
       <c r="DQ72" s="88"/>
       <c r="DR72" s="88"/>
     </row>
-    <row r="73" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="124">
         <v>68</v>
       </c>
@@ -18815,7 +18854,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="74" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="124">
         <v>69</v>
       </c>
@@ -19021,7 +19060,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="75" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="124">
         <v>70</v>
       </c>
@@ -19233,7 +19272,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="76" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="124">
         <v>71</v>
       </c>
@@ -19437,7 +19476,7 @@
       <c r="CL76" s="37"/>
       <c r="CM76" s="43"/>
     </row>
-    <row r="77" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="124">
         <v>72</v>
       </c>
@@ -19647,7 +19686,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="78" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="124">
         <v>73</v>
       </c>
@@ -19857,7 +19896,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="79" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="124">
         <v>74</v>
       </c>
@@ -20067,7 +20106,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="80" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="124">
         <v>75</v>
       </c>
@@ -20279,7 +20318,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="81" spans="1:91" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:91" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="124">
         <v>76</v>
       </c>
@@ -20499,7 +20538,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="82" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="124">
         <v>77</v>
       </c>
@@ -20711,7 +20750,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="83" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="124">
         <v>78</v>
       </c>
@@ -20919,7 +20958,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="84" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="124">
         <v>79</v>
       </c>
@@ -21129,7 +21168,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="85" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="124">
         <v>79</v>
       </c>
@@ -21339,7 +21378,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="86" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="124">
         <v>80</v>
       </c>
@@ -21549,7 +21588,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="87" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="124">
         <v>81</v>
       </c>
@@ -21757,7 +21796,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="88" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="124">
         <v>82</v>
       </c>
@@ -21969,7 +22008,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="89" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="124">
         <v>83</v>
       </c>
@@ -22177,7 +22216,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="90" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="124">
         <v>84</v>
       </c>
@@ -22385,7 +22424,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="91" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="124">
         <v>85</v>
       </c>
@@ -22595,7 +22634,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="92" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="124">
         <v>86</v>
       </c>
@@ -22807,7 +22846,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="93" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="136">
         <v>87</v>
       </c>
@@ -23008,12 +23047,12 @@
         <v>204</v>
       </c>
       <c r="CK93" s="37" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="CL93" s="37"/>
       <c r="CM93" s="43"/>
     </row>
-    <row r="94" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="136">
         <v>88</v>
       </c>
@@ -23039,7 +23078,7 @@
         <v>887</v>
       </c>
       <c r="I94" s="37" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="J94" s="3">
         <v>29.2</v>
@@ -23069,7 +23108,7 @@
         <v>-62.5</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="T94" s="3">
         <v>15</v>
@@ -23209,7 +23248,7 @@
         <v>700</v>
       </c>
       <c r="CH94" s="3" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="CI94" s="3" t="s">
         <v>668</v>
@@ -23218,16 +23257,16 @@
         <v>204</v>
       </c>
       <c r="CK94" s="37" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="CL94" s="37" t="s">
         <v>727</v>
       </c>
       <c r="CM94" s="43" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
-    <row r="95" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="136">
         <v>89</v>
       </c>
@@ -23253,7 +23292,7 @@
         <v>887</v>
       </c>
       <c r="I95" s="37" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="J95" s="3">
         <v>29.1</v>
@@ -23283,7 +23322,7 @@
         <v>-62.48</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="T95" s="3">
         <v>15</v>
@@ -23423,7 +23462,7 @@
         <v>803</v>
       </c>
       <c r="CH95" s="3" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="CI95" s="3" t="s">
         <v>668</v>
@@ -23432,58 +23471,135 @@
         <v>204</v>
       </c>
       <c r="CK95" s="37" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="CL95" s="37"/>
       <c r="CM95" s="43" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="96" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="136"/>
-      <c r="B96" s="136"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="35"/>
-      <c r="G96" s="35"/>
-      <c r="H96" s="35"/>
-      <c r="I96" s="37"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="35"/>
-      <c r="M96" s="35"/>
-      <c r="N96" s="3"/>
-      <c r="O96" s="37"/>
-      <c r="P96" s="37"/>
-      <c r="Q96" s="37"/>
-      <c r="R96" s="37"/>
-      <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="37"/>
-      <c r="Y96" s="37"/>
+    <row r="96" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="136">
+        <v>90</v>
+      </c>
+      <c r="B96" s="136">
+        <v>4</v>
+      </c>
+      <c r="C96" s="35">
+        <v>20260508</v>
+      </c>
+      <c r="D96" s="35">
+        <v>20260525</v>
+      </c>
+      <c r="E96" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="35">
+        <v>151</v>
+      </c>
+      <c r="G96" s="35">
+        <v>4800925</v>
+      </c>
+      <c r="H96" s="35" t="s">
+        <v>887</v>
+      </c>
+      <c r="I96" s="37" t="s">
+        <v>906</v>
+      </c>
+      <c r="J96" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="K96" s="3">
+        <v>25.5</v>
+      </c>
+      <c r="L96" s="35">
+        <v>44.520600000000002</v>
+      </c>
+      <c r="M96" s="35">
+        <v>-63.405700000000003</v>
+      </c>
+      <c r="N96" s="137">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="O96" s="37">
+        <v>43.49</v>
+      </c>
+      <c r="P96" s="37">
+        <v>-63.41</v>
+      </c>
+      <c r="Q96" s="37">
+        <v>44.53</v>
+      </c>
+      <c r="R96" s="37">
+        <v>-62.47</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="T96" s="3">
+        <v>17</v>
+      </c>
+      <c r="U96" s="3">
+        <v>332</v>
+      </c>
+      <c r="V96" s="3">
+        <v>781</v>
+      </c>
+      <c r="W96" s="3">
+        <f>V96*2-4</f>
+        <v>1558</v>
+      </c>
+      <c r="X96" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y96" s="37" t="s">
+        <v>227</v>
+      </c>
       <c r="Z96" s="37"/>
       <c r="AA96" s="37"/>
       <c r="AB96" s="37"/>
       <c r="AC96" s="37"/>
-      <c r="AD96" s="37"/>
-      <c r="AE96" s="37"/>
+      <c r="AD96" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="AE96" s="37" t="s">
+        <v>182</v>
+      </c>
       <c r="AF96" s="37"/>
       <c r="AG96" s="37"/>
-      <c r="AH96" s="37"/>
-      <c r="AI96" s="37"/>
-      <c r="AJ96" s="3"/>
-      <c r="AK96" s="3"/>
-      <c r="AL96" s="3"/>
-      <c r="AM96" s="3"/>
-      <c r="AN96" s="37"/>
-      <c r="AO96" s="37"/>
-      <c r="AP96" s="37"/>
-      <c r="AQ96" s="37"/>
-      <c r="AR96" s="35"/>
+      <c r="AH96" s="37">
+        <v>10</v>
+      </c>
+      <c r="AI96" s="37" t="s">
+        <v>909</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>2</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>2</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>1024.4000000000001</v>
+      </c>
+      <c r="AN96" s="37">
+        <v>20260421</v>
+      </c>
+      <c r="AO96" s="37">
+        <v>2</v>
+      </c>
+      <c r="AP96" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ96" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR96" s="35">
+        <v>163</v>
+      </c>
       <c r="AS96" s="34"/>
       <c r="AT96" s="38"/>
       <c r="AU96" s="38"/>
@@ -23498,85 +23614,206 @@
       <c r="BD96" s="38"/>
       <c r="BE96" s="38"/>
       <c r="BF96" s="38"/>
-      <c r="BG96" s="38"/>
-      <c r="BH96" s="38"/>
-      <c r="BI96" s="38"/>
-      <c r="BJ96" s="38"/>
-      <c r="BK96" s="46"/>
-      <c r="BL96" s="38"/>
+      <c r="BG96" s="38" t="s">
+        <v>869</v>
+      </c>
+      <c r="BH96" s="38" t="s">
+        <v>891</v>
+      </c>
+      <c r="BI96" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ96" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK96" s="46" t="s">
+        <v>870</v>
+      </c>
+      <c r="BL96" s="38" t="s">
+        <v>892</v>
+      </c>
       <c r="BM96" s="38"/>
-      <c r="BN96" s="38"/>
-      <c r="BO96" s="38"/>
+      <c r="BN96" s="38" t="s">
+        <v>893</v>
+      </c>
+      <c r="BO96" s="38" t="s">
+        <v>894</v>
+      </c>
       <c r="BP96" s="38"/>
       <c r="BQ96" s="38"/>
       <c r="BR96" s="38"/>
       <c r="BS96" s="38"/>
       <c r="BT96" s="38"/>
-      <c r="BU96" s="38"/>
-      <c r="BV96" s="38"/>
-      <c r="BW96" s="38"/>
-      <c r="BX96" s="38"/>
-      <c r="BY96" s="34"/>
-      <c r="BZ96" s="96"/>
-      <c r="CA96" s="96"/>
-      <c r="CB96" s="96"/>
-      <c r="CC96" s="96"/>
-      <c r="CD96" s="38"/>
-      <c r="CE96" s="167"/>
-      <c r="CF96" s="38"/>
-      <c r="CG96" s="38"/>
+      <c r="BU96" s="38" t="s">
+        <v>871</v>
+      </c>
+      <c r="BV96" s="38" t="s">
+        <v>886</v>
+      </c>
+      <c r="BW96" s="38" t="s">
+        <v>873</v>
+      </c>
+      <c r="BX96" s="38" t="s">
+        <v>895</v>
+      </c>
+      <c r="BY96" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BZ96" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="CA96" s="96" t="s">
+        <v>858</v>
+      </c>
+      <c r="CB96" s="96" t="s">
+        <v>845</v>
+      </c>
+      <c r="CC96" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="CD96" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="CE96" s="167" t="s">
+        <v>746</v>
+      </c>
+      <c r="CF96" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="CG96" s="38" t="s">
+        <v>188</v>
+      </c>
       <c r="CH96" s="3"/>
-      <c r="CI96" s="3"/>
-      <c r="CJ96" s="3"/>
-      <c r="CK96" s="37"/>
+      <c r="CI96" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CJ96" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK96" s="37" t="s">
+        <v>908</v>
+      </c>
       <c r="CL96" s="37"/>
-      <c r="CM96" s="43"/>
+      <c r="CM96" s="43" t="s">
+        <v>910</v>
+      </c>
     </row>
-    <row r="97" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="136"/>
+    <row r="97" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="136">
+        <v>91</v>
+      </c>
       <c r="B97" s="136"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="37"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="35"/>
-      <c r="M97" s="35"/>
-      <c r="N97" s="3"/>
-      <c r="O97" s="37"/>
-      <c r="P97" s="37"/>
-      <c r="Q97" s="37"/>
-      <c r="R97" s="37"/>
-      <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="37"/>
-      <c r="Y97" s="37"/>
+      <c r="C97" s="35">
+        <v>20260525</v>
+      </c>
+      <c r="D97" s="35">
+        <v>20260615</v>
+      </c>
+      <c r="E97" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="35">
+        <v>92</v>
+      </c>
+      <c r="G97" s="35">
+        <v>4800926</v>
+      </c>
+      <c r="H97" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="37" t="s">
+        <v>905</v>
+      </c>
+      <c r="J97" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="K97" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="L97" s="35">
+        <v>44.494599999999998</v>
+      </c>
+      <c r="M97" s="35">
+        <v>-63.396299999999997</v>
+      </c>
+      <c r="N97" s="137">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="O97" s="37">
+        <v>42.47</v>
+      </c>
+      <c r="P97" s="37">
+        <v>-63.4</v>
+      </c>
+      <c r="Q97" s="37">
+        <v>44.5</v>
+      </c>
+      <c r="R97" s="37">
+        <v>-61.43</v>
+      </c>
+      <c r="S97" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="T97" s="3">
+        <v>21</v>
+      </c>
+      <c r="U97" s="3">
+        <v>574</v>
+      </c>
+      <c r="V97" s="3">
+        <v>915</v>
+      </c>
+      <c r="W97" s="3">
+        <f>V97*2-4</f>
+        <v>1826</v>
+      </c>
+      <c r="X97" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y97" s="37">
+        <v>1</v>
+      </c>
       <c r="Z97" s="37"/>
-      <c r="AA97" s="37"/>
+      <c r="AA97" s="37" t="s">
+        <v>182</v>
+      </c>
       <c r="AB97" s="37"/>
       <c r="AC97" s="37"/>
-      <c r="AD97" s="37"/>
+      <c r="AD97" s="37" t="s">
+        <v>776</v>
+      </c>
       <c r="AE97" s="37"/>
       <c r="AF97" s="37"/>
       <c r="AG97" s="37"/>
       <c r="AH97" s="37"/>
       <c r="AI97" s="37"/>
-      <c r="AJ97" s="3"/>
-      <c r="AK97" s="3"/>
-      <c r="AL97" s="3"/>
-      <c r="AM97" s="3"/>
-      <c r="AN97" s="37"/>
-      <c r="AO97" s="37"/>
-      <c r="AP97" s="37"/>
-      <c r="AQ97" s="37"/>
-      <c r="AR97" s="35"/>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>1024.2</v>
+      </c>
+      <c r="AN97" s="37">
+        <v>20260512</v>
+      </c>
+      <c r="AO97" s="37">
+        <v>1</v>
+      </c>
+      <c r="AP97" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ97" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR97" s="35">
+        <v>29</v>
+      </c>
       <c r="AS97" s="34"/>
       <c r="AT97" s="38"/>
       <c r="AU97" s="38"/>
@@ -23586,17 +23823,35 @@
       <c r="AY97" s="38"/>
       <c r="AZ97" s="38"/>
       <c r="BA97" s="38"/>
-      <c r="BB97" s="34"/>
-      <c r="BC97" s="38"/>
-      <c r="BD97" s="38"/>
+      <c r="BB97" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC97" s="39">
+        <v>45631</v>
+      </c>
+      <c r="BD97" s="38" t="s">
+        <v>459</v>
+      </c>
       <c r="BE97" s="38"/>
       <c r="BF97" s="38"/>
-      <c r="BG97" s="38"/>
-      <c r="BH97" s="38"/>
-      <c r="BI97" s="38"/>
-      <c r="BJ97" s="38"/>
-      <c r="BK97" s="38"/>
-      <c r="BL97" s="38"/>
+      <c r="BG97" s="38" t="s">
+        <v>759</v>
+      </c>
+      <c r="BH97" s="38" t="s">
+        <v>780</v>
+      </c>
+      <c r="BI97" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ97" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK97" s="38" t="s">
+        <v>768</v>
+      </c>
+      <c r="BL97" s="38" t="s">
+        <v>815</v>
+      </c>
       <c r="BM97" s="38"/>
       <c r="BN97" s="38"/>
       <c r="BO97" s="38"/>
@@ -23609,28 +23864,58 @@
       <c r="BV97" s="38"/>
       <c r="BW97" s="38"/>
       <c r="BX97" s="38"/>
-      <c r="BY97" s="34"/>
-      <c r="BZ97" s="96"/>
-      <c r="CA97" s="96"/>
-      <c r="CB97" s="96"/>
-      <c r="CC97" s="96"/>
-      <c r="CD97" s="38"/>
-      <c r="CE97" s="144"/>
-      <c r="CF97" s="38"/>
-      <c r="CG97" s="38"/>
+      <c r="BY97" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BZ97" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="CA97" s="96" t="s">
+        <v>889</v>
+      </c>
+      <c r="CB97" s="96" t="s">
+        <v>165</v>
+      </c>
+      <c r="CC97" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="CD97" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE97" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="CF97" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG97" s="38" t="s">
+        <v>803</v>
+      </c>
       <c r="CH97" s="3"/>
-      <c r="CI97" s="35"/>
-      <c r="CJ97" s="35"/>
-      <c r="CK97" s="37"/>
+      <c r="CI97" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CJ97" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK97" s="37" t="s">
+        <v>196</v>
+      </c>
       <c r="CL97" s="37"/>
-      <c r="CM97" s="43"/>
+      <c r="CM97" s="43" t="s">
+        <v>911</v>
+      </c>
     </row>
-    <row r="98" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="136"/>
+    <row r="98" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="136">
+        <v>92</v>
+      </c>
       <c r="B98" s="136"/>
       <c r="C98" s="35"/>
       <c r="D98" s="35"/>
-      <c r="E98" s="35"/>
+      <c r="E98" s="35" t="s">
+        <v>912</v>
+      </c>
       <c r="F98" s="35"/>
       <c r="G98" s="35"/>
       <c r="H98" s="35"/>
@@ -23639,7 +23924,7 @@
       <c r="K98" s="3"/>
       <c r="L98" s="35"/>
       <c r="M98" s="35"/>
-      <c r="N98" s="3"/>
+      <c r="N98" s="137"/>
       <c r="O98" s="37"/>
       <c r="P98" s="37"/>
       <c r="Q98" s="37"/>
@@ -23664,7 +23949,9 @@
       <c r="AJ98" s="3"/>
       <c r="AK98" s="3"/>
       <c r="AL98" s="3"/>
-      <c r="AM98" s="3"/>
+      <c r="AM98" s="3">
+        <v>1023</v>
+      </c>
       <c r="AN98" s="37"/>
       <c r="AO98" s="37"/>
       <c r="AP98" s="37"/>
@@ -23680,7 +23967,7 @@
       <c r="AZ98" s="38"/>
       <c r="BA98" s="38"/>
       <c r="BB98" s="34"/>
-      <c r="BC98" s="38"/>
+      <c r="BC98" s="39"/>
       <c r="BD98" s="38"/>
       <c r="BE98" s="38"/>
       <c r="BF98" s="38"/>
@@ -23707,216 +23994,208 @@
       <c r="CA98" s="96"/>
       <c r="CB98" s="96"/>
       <c r="CC98" s="96"/>
-      <c r="CD98" s="38"/>
-      <c r="CE98" s="144"/>
+      <c r="CD98" s="40"/>
+      <c r="CE98" s="40"/>
       <c r="CF98" s="38"/>
       <c r="CG98" s="38"/>
       <c r="CH98" s="3"/>
-      <c r="CI98" s="35"/>
-      <c r="CJ98" s="35"/>
+      <c r="CI98" s="3"/>
+      <c r="CJ98" s="3"/>
       <c r="CK98" s="37"/>
       <c r="CL98" s="37"/>
       <c r="CM98" s="43"/>
     </row>
-    <row r="99" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="116"/>
-      <c r="D99" s="116"/>
-      <c r="E99" s="116"/>
-      <c r="F99" s="116"/>
-      <c r="G99" s="116"/>
-      <c r="H99" s="116"/>
-      <c r="I99" s="77"/>
-      <c r="L99" s="116"/>
-      <c r="M99" s="116"/>
-      <c r="O99" s="77"/>
-      <c r="P99" s="77"/>
-      <c r="Q99" s="77"/>
-      <c r="R99" s="77"/>
-      <c r="X99" s="77"/>
-      <c r="Y99" s="77"/>
-      <c r="Z99" s="77"/>
-      <c r="AA99" s="77"/>
-      <c r="AB99" s="77"/>
-      <c r="AC99" s="77"/>
-      <c r="AD99" s="77"/>
-      <c r="AE99" s="77"/>
-      <c r="AF99" s="77"/>
-      <c r="AG99" s="77"/>
-      <c r="AH99" s="77"/>
-      <c r="AI99" s="77"/>
-      <c r="AN99" s="77"/>
-      <c r="AO99" s="25" t="s">
-        <v>859</v>
-      </c>
-      <c r="AP99" s="77"/>
-      <c r="AQ99" s="77"/>
-      <c r="AR99" s="116"/>
-      <c r="AS99" s="27"/>
-      <c r="AT99" s="26"/>
-      <c r="AU99" s="78"/>
-      <c r="AV99" s="117"/>
-      <c r="AW99" s="27"/>
-      <c r="AX99" s="26"/>
-      <c r="AY99" s="78"/>
-      <c r="AZ99" s="78"/>
-      <c r="BA99" s="78"/>
-      <c r="BB99" s="117"/>
-      <c r="BC99" s="78"/>
-      <c r="BD99" s="78"/>
-      <c r="BE99" s="78"/>
-      <c r="BF99" s="145" t="s">
-        <v>762</v>
-      </c>
-      <c r="BG99" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="BH99" s="78" t="s">
-        <v>773</v>
-      </c>
-      <c r="BI99" s="78"/>
-      <c r="BJ99" s="78"/>
-      <c r="BK99" s="168" t="s">
-        <v>789</v>
-      </c>
-      <c r="BL99" s="78"/>
-      <c r="BM99" s="78"/>
-      <c r="BN99" s="78"/>
-      <c r="BO99" s="78"/>
-      <c r="BP99" s="78"/>
-      <c r="BQ99" s="78"/>
-      <c r="BR99" s="78"/>
-      <c r="BS99" s="78"/>
-      <c r="BT99" s="78"/>
-      <c r="BU99" s="78"/>
-      <c r="BV99" s="78"/>
-      <c r="BW99" s="78"/>
-      <c r="BX99" s="78"/>
-      <c r="BY99" s="117"/>
-      <c r="BZ99" s="118" t="s">
-        <v>831</v>
-      </c>
-      <c r="CA99" s="118"/>
-      <c r="CB99" s="118"/>
-      <c r="CC99" s="118"/>
-      <c r="CD99" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="CE99" s="160" t="s">
-        <v>747</v>
-      </c>
-      <c r="CF99" s="40" t="s">
-        <v>885</v>
-      </c>
-      <c r="CG99" s="40"/>
-      <c r="CH99" s="44"/>
-      <c r="CI99" s="121"/>
-      <c r="CJ99" s="45"/>
-      <c r="CK99" s="77"/>
-      <c r="CL99" s="77" t="s">
-        <v>820</v>
-      </c>
-      <c r="CM99" s="119"/>
+    <row r="99" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="136">
+        <v>93</v>
+      </c>
+      <c r="B99" s="136"/>
+      <c r="C99" s="35"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="35"/>
+      <c r="G99" s="35"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="37"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="35"/>
+      <c r="M99" s="35"/>
+      <c r="N99" s="137"/>
+      <c r="O99" s="37"/>
+      <c r="P99" s="37"/>
+      <c r="Q99" s="37"/>
+      <c r="R99" s="37"/>
+      <c r="S99" s="3"/>
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3"/>
+      <c r="W99" s="3"/>
+      <c r="X99" s="37"/>
+      <c r="Y99" s="37"/>
+      <c r="Z99" s="37"/>
+      <c r="AA99" s="37"/>
+      <c r="AB99" s="37"/>
+      <c r="AC99" s="37"/>
+      <c r="AD99" s="37"/>
+      <c r="AE99" s="37"/>
+      <c r="AF99" s="37"/>
+      <c r="AG99" s="37"/>
+      <c r="AH99" s="37"/>
+      <c r="AI99" s="37"/>
+      <c r="AJ99" s="3"/>
+      <c r="AK99" s="3"/>
+      <c r="AL99" s="3"/>
+      <c r="AM99" s="3"/>
+      <c r="AN99" s="37"/>
+      <c r="AO99" s="37"/>
+      <c r="AP99" s="37"/>
+      <c r="AQ99" s="37"/>
+      <c r="AR99" s="35"/>
+      <c r="AS99" s="34"/>
+      <c r="AT99" s="38"/>
+      <c r="AU99" s="38"/>
+      <c r="AV99" s="34"/>
+      <c r="AW99" s="34"/>
+      <c r="AX99" s="38"/>
+      <c r="AY99" s="38"/>
+      <c r="AZ99" s="38"/>
+      <c r="BA99" s="38"/>
+      <c r="BB99" s="34"/>
+      <c r="BC99" s="39"/>
+      <c r="BD99" s="38"/>
+      <c r="BE99" s="38"/>
+      <c r="BF99" s="38"/>
+      <c r="BG99" s="38"/>
+      <c r="BH99" s="38"/>
+      <c r="BI99" s="38"/>
+      <c r="BJ99" s="38"/>
+      <c r="BK99" s="38"/>
+      <c r="BL99" s="38"/>
+      <c r="BM99" s="38"/>
+      <c r="BN99" s="38"/>
+      <c r="BO99" s="38"/>
+      <c r="BP99" s="38"/>
+      <c r="BQ99" s="38"/>
+      <c r="BR99" s="38"/>
+      <c r="BS99" s="38"/>
+      <c r="BT99" s="38"/>
+      <c r="BU99" s="38"/>
+      <c r="BV99" s="38"/>
+      <c r="BW99" s="38"/>
+      <c r="BX99" s="38"/>
+      <c r="BY99" s="34"/>
+      <c r="BZ99" s="96"/>
+      <c r="CA99" s="96"/>
+      <c r="CB99" s="96"/>
+      <c r="CC99" s="96"/>
+      <c r="CD99" s="40"/>
+      <c r="CE99" s="40"/>
+      <c r="CF99" s="38"/>
+      <c r="CG99" s="38"/>
+      <c r="CH99" s="3"/>
+      <c r="CI99" s="3"/>
+      <c r="CJ99" s="3"/>
+      <c r="CK99" s="37"/>
+      <c r="CL99" s="37"/>
+      <c r="CM99" s="43"/>
     </row>
-    <row r="100" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C100" s="116"/>
-      <c r="D100" s="116"/>
-      <c r="E100" s="116"/>
-      <c r="F100" s="116"/>
-      <c r="G100" s="116"/>
-      <c r="H100" s="116"/>
-      <c r="I100" s="77"/>
-      <c r="L100" s="116"/>
-      <c r="M100" s="116"/>
-      <c r="O100" s="77"/>
-      <c r="P100" s="77"/>
-      <c r="Q100" s="77"/>
-      <c r="R100" s="77"/>
-      <c r="X100" s="77"/>
-      <c r="Y100" s="77"/>
-      <c r="Z100" s="77"/>
-      <c r="AA100" s="77"/>
-      <c r="AB100" s="77"/>
-      <c r="AC100" s="77"/>
-      <c r="AD100" s="77"/>
-      <c r="AE100" s="77"/>
-      <c r="AF100" s="77"/>
-      <c r="AG100" s="77"/>
-      <c r="AH100" s="77"/>
-      <c r="AI100" s="77"/>
-      <c r="AN100" s="77"/>
-      <c r="AO100" s="77"/>
-      <c r="AP100" s="77"/>
-      <c r="AQ100" s="77"/>
-      <c r="AR100" s="116">
-        <v>161</v>
-      </c>
-      <c r="AS100" s="27"/>
-      <c r="AT100" s="26"/>
-      <c r="AU100" s="78"/>
-      <c r="AV100" s="117"/>
-      <c r="AW100" s="27"/>
-      <c r="AX100" s="26"/>
-      <c r="AY100" s="78"/>
-      <c r="AZ100" s="78"/>
-      <c r="BA100" s="78"/>
-      <c r="BB100" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC100" s="26" t="s">
-        <v>751</v>
-      </c>
-      <c r="BD100" s="78" t="s">
-        <v>825</v>
-      </c>
-      <c r="BE100" s="78"/>
-      <c r="BF100" s="145"/>
-      <c r="BG100" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="BH100" s="78" t="s">
-        <v>774</v>
-      </c>
-      <c r="BI100" s="78"/>
-      <c r="BJ100" s="78"/>
-      <c r="BK100" s="168" t="s">
-        <v>790</v>
-      </c>
-      <c r="BL100" s="78"/>
-      <c r="BM100" s="78"/>
-      <c r="BN100" s="78"/>
-      <c r="BO100" s="78"/>
-      <c r="BP100" s="78"/>
-      <c r="BQ100" s="78"/>
-      <c r="BR100" s="78"/>
-      <c r="BS100" s="78"/>
-      <c r="BT100" s="78"/>
-      <c r="BU100" s="78"/>
-      <c r="BV100" s="78"/>
-      <c r="BW100" s="78"/>
-      <c r="BX100" s="78"/>
-      <c r="BY100" s="117"/>
-      <c r="BZ100" s="118" t="s">
-        <v>832</v>
-      </c>
-      <c r="CA100" s="118"/>
-      <c r="CB100" s="118"/>
-      <c r="CC100" s="118"/>
-      <c r="CD100" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="CE100" s="143" t="s">
-        <v>586</v>
-      </c>
+    <row r="100" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="136"/>
+      <c r="B100" s="136"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="35"/>
+      <c r="F100" s="35"/>
+      <c r="G100" s="35"/>
+      <c r="H100" s="35"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="35"/>
+      <c r="M100" s="35"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
+      <c r="R100" s="37"/>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="37"/>
+      <c r="Y100" s="37"/>
+      <c r="Z100" s="37"/>
+      <c r="AA100" s="37"/>
+      <c r="AB100" s="37"/>
+      <c r="AC100" s="37"/>
+      <c r="AD100" s="37"/>
+      <c r="AE100" s="37"/>
+      <c r="AF100" s="37"/>
+      <c r="AG100" s="37"/>
+      <c r="AH100" s="37"/>
+      <c r="AI100" s="37"/>
+      <c r="AJ100" s="3"/>
+      <c r="AK100" s="3"/>
+      <c r="AL100" s="3"/>
+      <c r="AM100" s="3"/>
+      <c r="AN100" s="37"/>
+      <c r="AO100" s="37"/>
+      <c r="AP100" s="37"/>
+      <c r="AQ100" s="37"/>
+      <c r="AR100" s="35"/>
+      <c r="AS100" s="34"/>
+      <c r="AT100" s="38"/>
+      <c r="AU100" s="38"/>
+      <c r="AV100" s="34"/>
+      <c r="AW100" s="34"/>
+      <c r="AX100" s="38"/>
+      <c r="AY100" s="38"/>
+      <c r="AZ100" s="38"/>
+      <c r="BA100" s="38"/>
+      <c r="BB100" s="34"/>
+      <c r="BC100" s="38"/>
+      <c r="BD100" s="38"/>
+      <c r="BE100" s="38"/>
+      <c r="BF100" s="38"/>
+      <c r="BG100" s="38"/>
+      <c r="BH100" s="38"/>
+      <c r="BI100" s="38"/>
+      <c r="BJ100" s="38"/>
+      <c r="BK100" s="38"/>
+      <c r="BL100" s="38"/>
+      <c r="BM100" s="38"/>
+      <c r="BN100" s="38"/>
+      <c r="BO100" s="38"/>
+      <c r="BP100" s="38"/>
+      <c r="BQ100" s="38"/>
+      <c r="BR100" s="38"/>
+      <c r="BS100" s="38"/>
+      <c r="BT100" s="38"/>
+      <c r="BU100" s="38"/>
+      <c r="BV100" s="38"/>
+      <c r="BW100" s="38"/>
+      <c r="BX100" s="38"/>
+      <c r="BY100" s="34"/>
+      <c r="BZ100" s="96"/>
+      <c r="CA100" s="96"/>
+      <c r="CB100" s="96"/>
+      <c r="CC100" s="96"/>
+      <c r="CD100" s="38"/>
+      <c r="CE100" s="144"/>
       <c r="CF100" s="38"/>
       <c r="CG100" s="38"/>
       <c r="CH100" s="3"/>
-      <c r="CI100" s="120"/>
+      <c r="CI100" s="35"/>
       <c r="CJ100" s="35"/>
-      <c r="CK100" s="77"/>
-      <c r="CL100" s="77"/>
-      <c r="CM100" s="119"/>
+      <c r="CK100" s="37"/>
+      <c r="CL100" s="37"/>
+      <c r="CM100" s="43"/>
     </row>
-    <row r="101" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C101" s="116"/>
       <c r="D101" s="116"/>
       <c r="E101" s="116"/>
@@ -23943,30 +24222,30 @@
       <c r="AH101" s="77"/>
       <c r="AI101" s="77"/>
       <c r="AN101" s="77"/>
-      <c r="AO101" s="77"/>
+      <c r="AO101" s="25" t="s">
+        <v>859</v>
+      </c>
       <c r="AP101" s="77"/>
       <c r="AQ101" s="77"/>
-      <c r="AR101" s="116">
-        <v>162</v>
-      </c>
-      <c r="AS101" s="117"/>
-      <c r="AT101" s="78"/>
+      <c r="AR101" s="116"/>
+      <c r="AS101" s="27"/>
+      <c r="AT101" s="26"/>
       <c r="AU101" s="78"/>
       <c r="AV101" s="117"/>
-      <c r="AW101" s="117"/>
-      <c r="AX101" s="78"/>
+      <c r="AW101" s="27"/>
+      <c r="AX101" s="26"/>
       <c r="AY101" s="78"/>
       <c r="AZ101" s="78"/>
       <c r="BA101" s="78"/>
-      <c r="BB101" s="27"/>
-      <c r="BC101" s="26"/>
+      <c r="BB101" s="117"/>
+      <c r="BC101" s="78"/>
       <c r="BD101" s="78"/>
       <c r="BE101" s="78"/>
       <c r="BF101" s="145" t="s">
-        <v>761</v>
-      </c>
-      <c r="BG101" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
+      </c>
+      <c r="BG101" s="6" t="s">
+        <v>757</v>
       </c>
       <c r="BH101" s="78" t="s">
         <v>773</v>
@@ -23974,11 +24253,9 @@
       <c r="BI101" s="78"/>
       <c r="BJ101" s="78"/>
       <c r="BK101" s="168" t="s">
-        <v>768</v>
-      </c>
-      <c r="BL101" s="78" t="s">
-        <v>815</v>
-      </c>
+        <v>789</v>
+      </c>
+      <c r="BL101" s="78"/>
       <c r="BM101" s="78"/>
       <c r="BN101" s="78"/>
       <c r="BO101" s="78"/>
@@ -23992,26 +24269,32 @@
       <c r="BW101" s="78"/>
       <c r="BX101" s="78"/>
       <c r="BY101" s="117"/>
-      <c r="BZ101" s="118"/>
+      <c r="BZ101" s="118" t="s">
+        <v>831</v>
+      </c>
       <c r="CA101" s="118"/>
       <c r="CB101" s="118"/>
       <c r="CC101" s="118"/>
-      <c r="CD101" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="CE101" s="144" t="s">
-        <v>800</v>
-      </c>
-      <c r="CF101" s="133"/>
-      <c r="CG101" s="133"/>
-      <c r="CH101" s="134"/>
-      <c r="CI101" s="135"/>
-      <c r="CJ101" s="29"/>
+      <c r="CD101" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE101" s="160" t="s">
+        <v>747</v>
+      </c>
+      <c r="CF101" s="40" t="s">
+        <v>885</v>
+      </c>
+      <c r="CG101" s="40"/>
+      <c r="CH101" s="44"/>
+      <c r="CI101" s="121"/>
+      <c r="CJ101" s="45"/>
       <c r="CK101" s="77"/>
-      <c r="CL101" s="77"/>
+      <c r="CL101" s="77" t="s">
+        <v>820</v>
+      </c>
       <c r="CM101" s="119"/>
     </row>
-    <row r="102" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C102" s="116"/>
       <c r="D102" s="116"/>
       <c r="E102" s="116"/>
@@ -24025,6 +24308,14 @@
       <c r="P102" s="77"/>
       <c r="Q102" s="77"/>
       <c r="R102" s="77"/>
+      <c r="T102" s="115">
+        <f>SUM(T3:T97)</f>
+        <v>1786</v>
+      </c>
+      <c r="U102" s="115">
+        <f>SUM(U3:U97)</f>
+        <v>45727</v>
+      </c>
       <c r="X102" s="77"/>
       <c r="Y102" s="77"/>
       <c r="Z102" s="77"/>
@@ -24041,31 +24332,31 @@
       <c r="AO102" s="77"/>
       <c r="AP102" s="77"/>
       <c r="AQ102" s="77"/>
-      <c r="AR102" s="116" t="s">
-        <v>874</v>
-      </c>
-      <c r="AS102" s="117"/>
-      <c r="AT102" s="78"/>
+      <c r="AR102" s="116">
+        <v>161</v>
+      </c>
+      <c r="AS102" s="27"/>
+      <c r="AT102" s="26"/>
       <c r="AU102" s="78"/>
       <c r="AV102" s="117"/>
-      <c r="AW102" s="117"/>
-      <c r="AX102" s="78"/>
+      <c r="AW102" s="27"/>
+      <c r="AX102" s="26"/>
       <c r="AY102" s="78"/>
       <c r="AZ102" s="78"/>
       <c r="BA102" s="78"/>
-      <c r="BB102" s="117" t="s">
-        <v>79</v>
+      <c r="BB102" s="27" t="s">
+        <v>74</v>
       </c>
       <c r="BC102" s="26" t="s">
-        <v>826</v>
+        <v>751</v>
       </c>
       <c r="BD102" s="78" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="BE102" s="78"/>
-      <c r="BF102" s="78"/>
-      <c r="BG102" s="5" t="s">
-        <v>760</v>
+      <c r="BF102" s="145"/>
+      <c r="BG102" s="6" t="s">
+        <v>758</v>
       </c>
       <c r="BH102" s="78" t="s">
         <v>774</v>
@@ -24073,11 +24364,9 @@
       <c r="BI102" s="78"/>
       <c r="BJ102" s="78"/>
       <c r="BK102" s="168" t="s">
-        <v>769</v>
-      </c>
-      <c r="BL102" s="78" t="s">
-        <v>802</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="BL102" s="78"/>
       <c r="BM102" s="78"/>
       <c r="BN102" s="78"/>
       <c r="BO102" s="78"/>
@@ -24091,26 +24380,28 @@
       <c r="BW102" s="78"/>
       <c r="BX102" s="78"/>
       <c r="BY102" s="117"/>
-      <c r="BZ102" s="118"/>
+      <c r="BZ102" s="118" t="s">
+        <v>832</v>
+      </c>
       <c r="CA102" s="118"/>
       <c r="CB102" s="118"/>
       <c r="CC102" s="118"/>
       <c r="CD102" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="CE102" s="144" t="s">
-        <v>746</v>
+        <v>95</v>
+      </c>
+      <c r="CE102" s="143" t="s">
+        <v>586</v>
       </c>
       <c r="CF102" s="38"/>
       <c r="CG102" s="38"/>
       <c r="CH102" s="3"/>
-      <c r="CI102" s="29"/>
-      <c r="CJ102" s="93"/>
+      <c r="CI102" s="120"/>
+      <c r="CJ102" s="35"/>
       <c r="CK102" s="77"/>
       <c r="CL102" s="77"/>
       <c r="CM102" s="119"/>
     </row>
-    <row r="103" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C103" s="116"/>
       <c r="D103" s="116"/>
       <c r="E103" s="116"/>
@@ -24140,7 +24431,9 @@
       <c r="AO103" s="77"/>
       <c r="AP103" s="77"/>
       <c r="AQ103" s="77"/>
-      <c r="AR103" s="116"/>
+      <c r="AR103" s="116">
+        <v>162</v>
+      </c>
       <c r="AS103" s="117"/>
       <c r="AT103" s="78"/>
       <c r="AU103" s="78"/>
@@ -24150,42 +24443,38 @@
       <c r="AY103" s="78"/>
       <c r="AZ103" s="78"/>
       <c r="BA103" s="78"/>
-      <c r="BB103" s="117"/>
-      <c r="BC103" s="78"/>
+      <c r="BB103" s="27"/>
+      <c r="BC103" s="26"/>
       <c r="BD103" s="78"/>
       <c r="BE103" s="78"/>
-      <c r="BF103" s="78" t="s">
-        <v>868</v>
-      </c>
-      <c r="BG103" s="78" t="s">
-        <v>869</v>
-      </c>
-      <c r="BH103" s="78"/>
+      <c r="BF103" s="145" t="s">
+        <v>761</v>
+      </c>
+      <c r="BG103" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="BH103" s="78" t="s">
+        <v>773</v>
+      </c>
       <c r="BI103" s="78"/>
       <c r="BJ103" s="78"/>
       <c r="BK103" s="168" t="s">
-        <v>870</v>
-      </c>
-      <c r="BL103" s="78"/>
+        <v>768</v>
+      </c>
+      <c r="BL103" s="78" t="s">
+        <v>815</v>
+      </c>
       <c r="BM103" s="78"/>
-      <c r="BN103" s="78" t="s">
-        <v>872</v>
-      </c>
+      <c r="BN103" s="78"/>
       <c r="BO103" s="78"/>
       <c r="BP103" s="78"/>
       <c r="BQ103" s="78"/>
       <c r="BR103" s="78"/>
       <c r="BS103" s="78"/>
       <c r="BT103" s="78"/>
-      <c r="BU103" s="78" t="s">
-        <v>871</v>
-      </c>
-      <c r="BV103" s="78" t="s">
-        <v>886</v>
-      </c>
-      <c r="BW103" s="78" t="s">
-        <v>873</v>
-      </c>
+      <c r="BU103" s="78"/>
+      <c r="BV103" s="78"/>
+      <c r="BW103" s="78"/>
       <c r="BX103" s="78"/>
       <c r="BY103" s="117"/>
       <c r="BZ103" s="118"/>
@@ -24193,21 +24482,21 @@
       <c r="CB103" s="118"/>
       <c r="CC103" s="118"/>
       <c r="CD103" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="CE103" s="143" t="s">
-        <v>514</v>
-      </c>
-      <c r="CF103" s="38"/>
-      <c r="CG103" s="38"/>
-      <c r="CH103" s="3"/>
-      <c r="CI103" s="29"/>
+        <v>117</v>
+      </c>
+      <c r="CE103" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="CF103" s="133"/>
+      <c r="CG103" s="133"/>
+      <c r="CH103" s="134"/>
+      <c r="CI103" s="135"/>
       <c r="CJ103" s="29"/>
       <c r="CK103" s="77"/>
       <c r="CL103" s="77"/>
       <c r="CM103" s="119"/>
     </row>
-    <row r="104" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C104" s="116"/>
       <c r="D104" s="116"/>
       <c r="E104" s="116"/>
@@ -24237,7 +24526,9 @@
       <c r="AO104" s="77"/>
       <c r="AP104" s="77"/>
       <c r="AQ104" s="77"/>
-      <c r="AR104" s="116"/>
+      <c r="AR104" s="116" t="s">
+        <v>874</v>
+      </c>
       <c r="AS104" s="117"/>
       <c r="AT104" s="78"/>
       <c r="AU104" s="78"/>
@@ -24247,31 +24538,35 @@
       <c r="AY104" s="78"/>
       <c r="AZ104" s="78"/>
       <c r="BA104" s="78"/>
-      <c r="BB104" s="117"/>
-      <c r="BC104" s="78"/>
-      <c r="BD104" s="78"/>
+      <c r="BB104" s="117" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC104" s="26" t="s">
+        <v>826</v>
+      </c>
+      <c r="BD104" s="78" t="s">
+        <v>827</v>
+      </c>
       <c r="BE104" s="78"/>
-      <c r="BF104" s="78" t="s">
-        <v>875</v>
-      </c>
-      <c r="BG104" s="78" t="s">
-        <v>877</v>
-      </c>
-      <c r="BH104" s="78"/>
+      <c r="BF104" s="78"/>
+      <c r="BG104" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="BH104" s="78" t="s">
+        <v>774</v>
+      </c>
       <c r="BI104" s="78"/>
       <c r="BJ104" s="78"/>
       <c r="BK104" s="168" t="s">
-        <v>878</v>
-      </c>
-      <c r="BL104" s="78"/>
+        <v>769</v>
+      </c>
+      <c r="BL104" s="78" t="s">
+        <v>802</v>
+      </c>
       <c r="BM104" s="78"/>
-      <c r="BN104" s="78" t="s">
-        <v>879</v>
-      </c>
+      <c r="BN104" s="78"/>
       <c r="BO104" s="78"/>
-      <c r="BP104" s="78" t="s">
-        <v>880</v>
-      </c>
+      <c r="BP104" s="78"/>
       <c r="BQ104" s="78"/>
       <c r="BR104" s="78"/>
       <c r="BS104" s="78"/>
@@ -24286,21 +24581,21 @@
       <c r="CB104" s="118"/>
       <c r="CC104" s="118"/>
       <c r="CD104" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="CE104" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="CF104" s="46"/>
-      <c r="CG104" s="46"/>
-      <c r="CH104" s="48"/>
+        <v>245</v>
+      </c>
+      <c r="CE104" s="144" t="s">
+        <v>746</v>
+      </c>
+      <c r="CF104" s="38"/>
+      <c r="CG104" s="38"/>
+      <c r="CH104" s="3"/>
       <c r="CI104" s="29"/>
-      <c r="CJ104" s="29"/>
+      <c r="CJ104" s="93"/>
       <c r="CK104" s="77"/>
       <c r="CL104" s="77"/>
       <c r="CM104" s="119"/>
     </row>
-    <row r="105" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C105" s="116"/>
       <c r="D105" s="116"/>
       <c r="E105" s="116"/>
@@ -24345,54 +24640,59 @@
       <c r="BD105" s="78"/>
       <c r="BE105" s="78"/>
       <c r="BF105" s="78" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="BG105" s="78" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="BH105" s="78"/>
       <c r="BI105" s="78"/>
       <c r="BJ105" s="78"/>
       <c r="BK105" s="168" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="BL105" s="78"/>
       <c r="BM105" s="78"/>
       <c r="BN105" s="78" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="BO105" s="78"/>
-      <c r="BP105" s="78" t="s">
-        <v>881</v>
-      </c>
+      <c r="BP105" s="78"/>
       <c r="BQ105" s="78"/>
       <c r="BR105" s="78"/>
       <c r="BS105" s="78"/>
       <c r="BT105" s="78"/>
-      <c r="BU105" s="78"/>
-      <c r="BV105" s="78"/>
-      <c r="BW105" s="78"/>
+      <c r="BU105" s="78" t="s">
+        <v>871</v>
+      </c>
+      <c r="BV105" s="78" t="s">
+        <v>886</v>
+      </c>
+      <c r="BW105" s="78" t="s">
+        <v>873</v>
+      </c>
       <c r="BX105" s="78"/>
       <c r="BY105" s="117"/>
       <c r="BZ105" s="118"/>
       <c r="CA105" s="118"/>
       <c r="CB105" s="118"/>
       <c r="CC105" s="118"/>
-      <c r="CD105" s="46" t="s">
-        <v>841</v>
-      </c>
-      <c r="CE105" s="159" t="s">
-        <v>840</v>
-      </c>
-      <c r="CF105" s="78"/>
-      <c r="CG105" s="78"/>
-      <c r="CI105" s="116"/>
-      <c r="CJ105" s="116"/>
+      <c r="CD105" s="38" t="s">
+        <v>513</v>
+      </c>
+      <c r="CE105" s="143" t="s">
+        <v>514</v>
+      </c>
+      <c r="CF105" s="38"/>
+      <c r="CG105" s="38"/>
+      <c r="CH105" s="3"/>
+      <c r="CI105" s="29"/>
+      <c r="CJ105" s="29"/>
       <c r="CK105" s="77"/>
       <c r="CL105" s="77"/>
       <c r="CM105" s="119"/>
     </row>
-    <row r="106" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C106" s="116"/>
       <c r="D106" s="116"/>
       <c r="E106" s="116"/>
@@ -24436,17 +24736,27 @@
       <c r="BC106" s="78"/>
       <c r="BD106" s="78"/>
       <c r="BE106" s="78"/>
-      <c r="BF106" s="78"/>
-      <c r="BG106" s="78"/>
+      <c r="BF106" s="78" t="s">
+        <v>875</v>
+      </c>
+      <c r="BG106" s="78" t="s">
+        <v>877</v>
+      </c>
       <c r="BH106" s="78"/>
       <c r="BI106" s="78"/>
       <c r="BJ106" s="78"/>
-      <c r="BK106" s="78"/>
+      <c r="BK106" s="168" t="s">
+        <v>878</v>
+      </c>
       <c r="BL106" s="78"/>
       <c r="BM106" s="78"/>
-      <c r="BN106" s="78"/>
+      <c r="BN106" s="78" t="s">
+        <v>879</v>
+      </c>
       <c r="BO106" s="78"/>
-      <c r="BP106" s="78"/>
+      <c r="BP106" s="78" t="s">
+        <v>880</v>
+      </c>
       <c r="BQ106" s="78"/>
       <c r="BR106" s="78"/>
       <c r="BS106" s="78"/>
@@ -24460,19 +24770,194 @@
       <c r="CA106" s="118"/>
       <c r="CB106" s="118"/>
       <c r="CC106" s="118"/>
-      <c r="CD106" s="142">
-        <v>286370</v>
-      </c>
-      <c r="CE106" s="162" t="s">
-        <v>842</v>
-      </c>
-      <c r="CF106" s="78"/>
-      <c r="CG106" s="78"/>
-      <c r="CI106" s="116"/>
-      <c r="CJ106" s="116"/>
+      <c r="CD106" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="CE106" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="CF106" s="46"/>
+      <c r="CG106" s="46"/>
+      <c r="CH106" s="48"/>
+      <c r="CI106" s="29"/>
+      <c r="CJ106" s="29"/>
       <c r="CK106" s="77"/>
       <c r="CL106" s="77"/>
       <c r="CM106" s="119"/>
+    </row>
+    <row r="107" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C107" s="116"/>
+      <c r="D107" s="116"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="116"/>
+      <c r="H107" s="116"/>
+      <c r="I107" s="77"/>
+      <c r="L107" s="116"/>
+      <c r="M107" s="116"/>
+      <c r="O107" s="77"/>
+      <c r="P107" s="77"/>
+      <c r="Q107" s="77"/>
+      <c r="R107" s="77"/>
+      <c r="X107" s="77"/>
+      <c r="Y107" s="77"/>
+      <c r="Z107" s="77"/>
+      <c r="AA107" s="77"/>
+      <c r="AB107" s="77"/>
+      <c r="AC107" s="77"/>
+      <c r="AD107" s="77"/>
+      <c r="AE107" s="77"/>
+      <c r="AF107" s="77"/>
+      <c r="AG107" s="77"/>
+      <c r="AH107" s="77"/>
+      <c r="AI107" s="77"/>
+      <c r="AN107" s="77"/>
+      <c r="AO107" s="77"/>
+      <c r="AP107" s="77"/>
+      <c r="AQ107" s="77"/>
+      <c r="AR107" s="116"/>
+      <c r="AS107" s="117"/>
+      <c r="AT107" s="78"/>
+      <c r="AU107" s="78"/>
+      <c r="AV107" s="117"/>
+      <c r="AW107" s="117"/>
+      <c r="AX107" s="78"/>
+      <c r="AY107" s="78"/>
+      <c r="AZ107" s="78"/>
+      <c r="BA107" s="78"/>
+      <c r="BB107" s="117"/>
+      <c r="BC107" s="78"/>
+      <c r="BD107" s="78"/>
+      <c r="BE107" s="78"/>
+      <c r="BF107" s="78" t="s">
+        <v>876</v>
+      </c>
+      <c r="BG107" s="78" t="s">
+        <v>884</v>
+      </c>
+      <c r="BH107" s="78"/>
+      <c r="BI107" s="78"/>
+      <c r="BJ107" s="78"/>
+      <c r="BK107" s="168" t="s">
+        <v>882</v>
+      </c>
+      <c r="BL107" s="78"/>
+      <c r="BM107" s="78"/>
+      <c r="BN107" s="78" t="s">
+        <v>883</v>
+      </c>
+      <c r="BO107" s="78"/>
+      <c r="BP107" s="78" t="s">
+        <v>881</v>
+      </c>
+      <c r="BQ107" s="78"/>
+      <c r="BR107" s="78"/>
+      <c r="BS107" s="78"/>
+      <c r="BT107" s="78"/>
+      <c r="BU107" s="78"/>
+      <c r="BV107" s="78"/>
+      <c r="BW107" s="78"/>
+      <c r="BX107" s="78"/>
+      <c r="BY107" s="117"/>
+      <c r="BZ107" s="118"/>
+      <c r="CA107" s="118"/>
+      <c r="CB107" s="118"/>
+      <c r="CC107" s="118"/>
+      <c r="CD107" s="46" t="s">
+        <v>841</v>
+      </c>
+      <c r="CE107" s="159" t="s">
+        <v>840</v>
+      </c>
+      <c r="CF107" s="78"/>
+      <c r="CG107" s="78"/>
+      <c r="CI107" s="116"/>
+      <c r="CJ107" s="116"/>
+      <c r="CK107" s="77"/>
+      <c r="CL107" s="77"/>
+      <c r="CM107" s="119"/>
+    </row>
+    <row r="108" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C108" s="116"/>
+      <c r="D108" s="116"/>
+      <c r="E108" s="116"/>
+      <c r="F108" s="116"/>
+      <c r="G108" s="116"/>
+      <c r="H108" s="116"/>
+      <c r="I108" s="77"/>
+      <c r="L108" s="116"/>
+      <c r="M108" s="116"/>
+      <c r="O108" s="77"/>
+      <c r="P108" s="77"/>
+      <c r="Q108" s="77"/>
+      <c r="R108" s="77"/>
+      <c r="X108" s="77"/>
+      <c r="Y108" s="77"/>
+      <c r="Z108" s="77"/>
+      <c r="AA108" s="77"/>
+      <c r="AB108" s="77"/>
+      <c r="AC108" s="77"/>
+      <c r="AD108" s="77"/>
+      <c r="AE108" s="77"/>
+      <c r="AF108" s="77"/>
+      <c r="AG108" s="77"/>
+      <c r="AH108" s="77"/>
+      <c r="AI108" s="77"/>
+      <c r="AN108" s="77"/>
+      <c r="AO108" s="77"/>
+      <c r="AP108" s="77"/>
+      <c r="AQ108" s="77"/>
+      <c r="AR108" s="116"/>
+      <c r="AS108" s="117"/>
+      <c r="AT108" s="78"/>
+      <c r="AU108" s="78"/>
+      <c r="AV108" s="117"/>
+      <c r="AW108" s="117"/>
+      <c r="AX108" s="78"/>
+      <c r="AY108" s="78"/>
+      <c r="AZ108" s="78"/>
+      <c r="BA108" s="78"/>
+      <c r="BB108" s="117"/>
+      <c r="BC108" s="78"/>
+      <c r="BD108" s="78"/>
+      <c r="BE108" s="78"/>
+      <c r="BF108" s="78"/>
+      <c r="BG108" s="78"/>
+      <c r="BH108" s="78"/>
+      <c r="BI108" s="78"/>
+      <c r="BJ108" s="78"/>
+      <c r="BK108" s="78"/>
+      <c r="BL108" s="78"/>
+      <c r="BM108" s="78"/>
+      <c r="BN108" s="78"/>
+      <c r="BO108" s="78"/>
+      <c r="BP108" s="78"/>
+      <c r="BQ108" s="78"/>
+      <c r="BR108" s="78"/>
+      <c r="BS108" s="78"/>
+      <c r="BT108" s="78"/>
+      <c r="BU108" s="78"/>
+      <c r="BV108" s="78"/>
+      <c r="BW108" s="78"/>
+      <c r="BX108" s="78"/>
+      <c r="BY108" s="117"/>
+      <c r="BZ108" s="118"/>
+      <c r="CA108" s="118"/>
+      <c r="CB108" s="118"/>
+      <c r="CC108" s="118"/>
+      <c r="CD108" s="142">
+        <v>286370</v>
+      </c>
+      <c r="CE108" s="162" t="s">
+        <v>842</v>
+      </c>
+      <c r="CF108" s="78"/>
+      <c r="CG108" s="78"/>
+      <c r="CI108" s="116"/>
+      <c r="CJ108" s="116"/>
+      <c r="CK108" s="77"/>
+      <c r="CL108" s="77"/>
+      <c r="CM108" s="119"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -24487,17 +24972,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:E14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="73" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="107" t="s">
         <v>475</v>
       </c>
@@ -24514,7 +24999,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="104" t="s">
         <v>19</v>
       </c>
@@ -24531,7 +25016,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="34" t="s">
         <v>60</v>
       </c>
@@ -24548,7 +25033,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="111" t="s">
         <v>123</v>
       </c>
@@ -24565,7 +25050,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="34" t="s">
         <v>176</v>
       </c>
@@ -24582,7 +25067,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="111" t="s">
         <v>234</v>
       </c>
@@ -24599,7 +25084,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="111" t="s">
         <v>272</v>
       </c>
@@ -24616,7 +25101,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
         <v>373</v>
       </c>
@@ -24633,7 +25118,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="34" t="s">
         <v>433</v>
       </c>
@@ -24650,7 +25135,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="101"/>
     </row>
   </sheetData>
@@ -24665,16 +25150,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:F63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="128" t="s">
         <v>534</v>
       </c>
@@ -24691,7 +25176,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" s="41" t="s">
         <v>16</v>
       </c>
@@ -24708,7 +25193,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
         <v>17</v>
       </c>
@@ -24725,7 +25210,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="34" t="s">
         <v>23</v>
       </c>
@@ -24742,7 +25227,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="34" t="s">
         <v>30</v>
       </c>
@@ -24759,7 +25244,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="34" t="s">
         <v>31</v>
       </c>
@@ -24776,7 +25261,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="34" t="s">
         <v>33</v>
       </c>
@@ -24793,7 +25278,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="34" t="s">
         <v>45</v>
       </c>
@@ -24810,7 +25295,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="34" t="s">
         <v>50</v>
       </c>
@@ -24827,7 +25312,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="34" t="s">
         <v>54</v>
       </c>
@@ -24844,7 +25329,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="34" t="s">
         <v>54</v>
       </c>
@@ -24861,7 +25346,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="34" t="s">
         <v>63</v>
       </c>
@@ -24878,7 +25363,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="34" t="s">
         <v>65</v>
       </c>
@@ -24895,14 +25380,14 @@
         <v>533</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="126"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="34" t="s">
         <v>100</v>
       </c>
@@ -24919,7 +25404,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="34" t="s">
         <v>105</v>
       </c>
@@ -24936,7 +25421,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="34" t="s">
         <v>110</v>
       </c>
@@ -24953,7 +25438,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="34" t="s">
         <v>119</v>
       </c>
@@ -24970,7 +25455,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="34" t="s">
         <v>129</v>
       </c>
@@ -24987,7 +25472,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="34" t="s">
         <v>133</v>
       </c>
@@ -25004,7 +25489,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="34" t="s">
         <v>134</v>
       </c>
@@ -25021,7 +25506,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="34" t="s">
         <v>140</v>
       </c>
@@ -25038,7 +25523,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="34" t="s">
         <v>154</v>
       </c>
@@ -25055,7 +25540,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="34" t="s">
         <v>155</v>
       </c>
@@ -25072,7 +25557,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="34" t="s">
         <v>171</v>
       </c>
@@ -25089,7 +25574,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="34" t="s">
         <v>171</v>
       </c>
@@ -25106,7 +25591,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="34" t="s">
         <v>173</v>
       </c>
@@ -25123,7 +25608,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="34" t="s">
         <v>181</v>
       </c>
@@ -25140,7 +25625,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="34" t="s">
         <v>181</v>
       </c>
@@ -25157,7 +25642,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="34" t="s">
         <v>189</v>
       </c>
@@ -25174,14 +25659,14 @@
         <v>549</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="126"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="34" t="s">
         <v>214</v>
       </c>
@@ -25198,7 +25683,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="34" t="s">
         <v>224</v>
       </c>
@@ -25215,7 +25700,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="34" t="s">
         <v>248</v>
       </c>
@@ -25232,7 +25717,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="34" t="s">
         <v>257</v>
       </c>
@@ -25249,7 +25734,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="34" t="s">
         <v>257</v>
       </c>
@@ -25266,7 +25751,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="34" t="s">
         <v>266</v>
       </c>
@@ -25283,7 +25768,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="34" t="s">
         <v>273</v>
       </c>
@@ -25300,7 +25785,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="34" t="s">
         <v>280</v>
       </c>
@@ -25317,7 +25802,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="34" t="s">
         <v>282</v>
       </c>
@@ -25334,7 +25819,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="34" t="s">
         <v>293</v>
       </c>
@@ -25351,14 +25836,14 @@
         <v>564</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="126"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="34" t="s">
         <v>346</v>
       </c>
@@ -25375,7 +25860,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="34" t="s">
         <v>349</v>
       </c>
@@ -25392,7 +25877,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="34" t="s">
         <v>358</v>
       </c>
@@ -25409,7 +25894,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="34" t="s">
         <v>372</v>
       </c>
@@ -25426,7 +25911,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B47" s="34" t="s">
         <v>379</v>
       </c>
@@ -25443,7 +25928,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="34" t="s">
         <v>383</v>
       </c>
@@ -25460,7 +25945,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B49" s="34" t="s">
         <v>384</v>
       </c>
@@ -25477,7 +25962,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="34" t="s">
         <v>392</v>
       </c>
@@ -25494,7 +25979,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="34" t="s">
         <v>392</v>
       </c>
@@ -25511,7 +25996,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="34" t="s">
         <v>393</v>
       </c>
@@ -25528,7 +26013,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="34" t="s">
         <v>402</v>
       </c>
@@ -25545,7 +26030,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="34" t="s">
         <v>408</v>
       </c>
@@ -25562,7 +26047,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="34" t="s">
         <v>408</v>
       </c>
@@ -25579,7 +26064,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="34" t="s">
         <v>411</v>
       </c>
@@ -25596,7 +26081,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="34" t="s">
         <v>419</v>
       </c>
@@ -25613,14 +26098,14 @@
         <v>572</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
       <c r="F58" s="126"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="34" t="s">
         <v>432</v>
       </c>
@@ -25637,7 +26122,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3">
         <v>20220303</v>
       </c>
@@ -25654,7 +26139,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B61" s="3">
         <v>20220406</v>
       </c>
@@ -25671,7 +26156,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B62" s="3">
         <v>20220908</v>
       </c>
@@ -25688,7 +26173,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3">
         <v>20220915</v>
       </c>
@@ -25727,17 +26212,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13133089-9C8E-40DB-8C04-5B07C5991D49}">
   <dimension ref="B2:H13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.21875" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>807</v>
       </c>
@@ -25745,10 +26230,10 @@
         <v>808</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D3" s="156"/>
     </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="155" t="s">
         <v>805</v>
       </c>
@@ -25771,7 +26256,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="44">
         <v>28.9</v>
       </c>
@@ -25795,7 +26280,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>29</v>
       </c>
@@ -25819,7 +26304,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="3">
         <v>29.1</v>
       </c>
@@ -25843,7 +26328,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="154">
         <v>28.5</v>
       </c>
@@ -25867,7 +26352,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="3">
         <v>29.1</v>
       </c>
@@ -25891,7 +26376,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="3">
         <v>29.1</v>
       </c>
@@ -25915,7 +26400,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>29.2</v>
       </c>
@@ -25939,7 +26424,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <v>29.1</v>
       </c>
@@ -25963,7 +26448,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
         <v>809</v>
       </c>

--- a/initializationData/GliderMission.xlsx
+++ b/initializationData/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laytonc\Documents\GitHub\gliderMetadata\initializationData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91611377-07EB-4DC5-AA9E-E32006E32FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD59DD7-65F9-4ABD-83EA-03947DB6E811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24569,7 +24569,9 @@
     </row>
     <row r="98" spans="1:96" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="174"/>
-      <c r="B98" s="174"/>
+      <c r="B98" s="174">
+        <v>5</v>
+      </c>
       <c r="C98" s="35">
         <v>20260630</v>
       </c>
@@ -25318,9 +25320,7 @@
       <c r="CR102" s="43"/>
     </row>
     <row r="103" spans="1:96" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="133">
-        <v>96</v>
-      </c>
+      <c r="A103" s="133"/>
       <c r="B103" s="133"/>
       <c r="C103" s="35"/>
       <c r="D103" s="35"/>
@@ -25418,9 +25418,7 @@
       <c r="CR103" s="43"/>
     </row>
     <row r="104" spans="1:96" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="133">
-        <v>97</v>
-      </c>
+      <c r="A104" s="133"/>
       <c r="B104" s="133"/>
       <c r="C104" s="35"/>
       <c r="D104" s="35"/>
@@ -25518,9 +25516,7 @@
       <c r="CR104" s="43"/>
     </row>
     <row r="105" spans="1:96" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="133">
-        <v>98</v>
-      </c>
+      <c r="A105" s="133"/>
       <c r="B105" s="133"/>
       <c r="C105" s="35"/>
       <c r="D105" s="35"/>
@@ -25618,9 +25614,7 @@
       <c r="CR105" s="43"/>
     </row>
     <row r="106" spans="1:96" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="133">
-        <v>99</v>
-      </c>
+      <c r="A106" s="133"/>
       <c r="B106" s="133"/>
       <c r="C106" s="35"/>
       <c r="D106" s="35"/>
@@ -25718,9 +25712,7 @@
       <c r="CR106" s="43"/>
     </row>
     <row r="107" spans="1:96" s="172" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="163">
-        <v>100</v>
-      </c>
+      <c r="A107" s="163"/>
       <c r="B107" s="163"/>
       <c r="C107" s="164"/>
       <c r="D107" s="164"/>
